--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.reynaga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991E21F1-178E-4D54-92BC-149926FA1D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{9963C2FA-C7AC-4C2C-BC3F-F76FCFE9739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2536,6 +2536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2616,7 +2617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>290</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>290</v>
       </c>
@@ -2680,7 +2681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>290</v>
       </c>
@@ -2712,7 +2713,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>290</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>290</v>
       </c>
@@ -2776,7 +2777,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>290</v>
       </c>
@@ -2808,7 +2809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>290</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -2904,7 +2905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>289</v>
       </c>
@@ -2936,7 +2937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>289</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>289</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -3032,7 +3033,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -3064,7 +3065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>289</v>
       </c>
@@ -3122,13 +3123,13 @@
         <v>20</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>292</v>
       </c>
@@ -3160,7 +3161,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -3192,7 +3193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>292</v>
       </c>
@@ -3224,7 +3225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>292</v>
       </c>
@@ -3256,7 +3257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>292</v>
       </c>
@@ -3288,7 +3289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>292</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>292</v>
       </c>
@@ -3384,7 +3385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>295</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>295</v>
       </c>
@@ -3448,7 +3449,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>295</v>
       </c>
@@ -3480,7 +3481,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>295</v>
       </c>
@@ -3512,7 +3513,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>295</v>
       </c>
@@ -3544,7 +3545,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>295</v>
       </c>
@@ -3576,7 +3577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>295</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>296</v>
       </c>
@@ -3672,7 +3673,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>296</v>
       </c>
@@ -3704,7 +3705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>296</v>
       </c>
@@ -3736,7 +3737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>296</v>
       </c>
@@ -3768,7 +3769,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>296</v>
       </c>
@@ -3800,7 +3801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>296</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>296</v>
       </c>
@@ -3896,7 +3897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>291</v>
       </c>
@@ -3928,7 +3929,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -3960,7 +3961,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>291</v>
       </c>
@@ -3992,7 +3993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>291</v>
       </c>
@@ -4024,7 +4025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>291</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>291</v>
       </c>
@@ -4088,7 +4089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>291</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>293</v>
       </c>
@@ -4216,7 +4217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>293</v>
       </c>
@@ -4248,7 +4249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -4280,7 +4281,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>293</v>
       </c>
@@ -4312,7 +4313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>293</v>
       </c>
@@ -4344,7 +4345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>293</v>
       </c>
@@ -4408,7 +4409,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>294</v>
       </c>
@@ -4440,7 +4441,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>294</v>
       </c>
@@ -4472,7 +4473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>294</v>
       </c>
@@ -4504,7 +4505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>294</v>
       </c>
@@ -4536,7 +4537,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>294</v>
       </c>
@@ -4568,7 +4569,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>294</v>
       </c>
@@ -4600,7 +4601,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>294</v>
       </c>
@@ -4664,7 +4665,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>298</v>
       </c>
@@ -4696,7 +4697,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>298</v>
       </c>
@@ -4728,7 +4729,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>298</v>
       </c>
@@ -4760,7 +4761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>298</v>
       </c>
@@ -4792,7 +4793,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>298</v>
       </c>
@@ -4824,7 +4825,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>298</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>298</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>297</v>
       </c>
@@ -4952,7 +4953,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>297</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>297</v>
       </c>
@@ -5016,7 +5017,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>297</v>
       </c>
@@ -5048,7 +5049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>297</v>
       </c>
@@ -5080,7 +5081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>297</v>
       </c>
@@ -5112,7 +5113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>297</v>
       </c>
@@ -5145,7 +5146,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K81" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Análisis de gabinete"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{9963C2FA-C7AC-4C2C-BC3F-F76FCFE9739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A0D8F11F-9908-41BF-B81B-266AB3024C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2611,7 +2611,7 @@
         <v>17</v>
       </c>
       <c r="I2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>

--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A0D8F11F-9908-41BF-B81B-266AB3024C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{22219FAC-0A92-45F8-A9A9-E7907A117DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2536,7 +2536,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2611,13 +2610,13 @@
         <v>17</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>290</v>
       </c>
@@ -2649,7 +2648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>290</v>
       </c>
@@ -2681,7 +2680,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>290</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>290</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>290</v>
       </c>
@@ -2777,7 +2776,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>290</v>
       </c>
@@ -2809,7 +2808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>290</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -2905,7 +2904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>289</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>289</v>
       </c>
@@ -2969,7 +2968,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>289</v>
       </c>
@@ -3001,7 +3000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>289</v>
       </c>
@@ -3065,7 +3064,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>289</v>
       </c>
@@ -3129,7 +3128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>292</v>
       </c>
@@ -3161,7 +3160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>292</v>
       </c>
@@ -3193,7 +3192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>292</v>
       </c>
@@ -3225,7 +3224,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>292</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>292</v>
       </c>
@@ -3289,7 +3288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>292</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>292</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>295</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>295</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>295</v>
       </c>
@@ -3481,7 +3480,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>295</v>
       </c>
@@ -3513,7 +3512,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>295</v>
       </c>
@@ -3545,7 +3544,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>295</v>
       </c>
@@ -3577,7 +3576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>295</v>
       </c>
@@ -3641,7 +3640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>296</v>
       </c>
@@ -3673,7 +3672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>296</v>
       </c>
@@ -3705,7 +3704,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>296</v>
       </c>
@@ -3737,7 +3736,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>296</v>
       </c>
@@ -3769,7 +3768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>296</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>296</v>
       </c>
@@ -3833,7 +3832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>296</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>291</v>
       </c>
@@ -3929,7 +3928,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>291</v>
       </c>
@@ -3961,7 +3960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>291</v>
       </c>
@@ -3993,7 +3992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>291</v>
       </c>
@@ -4025,7 +4024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>291</v>
       </c>
@@ -4057,7 +4056,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>291</v>
       </c>
@@ -4089,7 +4088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>291</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -4185,7 +4184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>293</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>293</v>
       </c>
@@ -4249,7 +4248,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -4281,7 +4280,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>293</v>
       </c>
@@ -4313,7 +4312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>293</v>
       </c>
@@ -4345,7 +4344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>293</v>
       </c>
@@ -4409,7 +4408,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>294</v>
       </c>
@@ -4441,7 +4440,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>294</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>294</v>
       </c>
@@ -4505,7 +4504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>294</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>294</v>
       </c>
@@ -4569,7 +4568,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>294</v>
       </c>
@@ -4601,7 +4600,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>294</v>
       </c>
@@ -4665,7 +4664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>298</v>
       </c>
@@ -4697,7 +4696,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>298</v>
       </c>
@@ -4729,7 +4728,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>298</v>
       </c>
@@ -4761,7 +4760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>298</v>
       </c>
@@ -4793,7 +4792,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>298</v>
       </c>
@@ -4825,7 +4824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>298</v>
       </c>
@@ -4857,7 +4856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>298</v>
       </c>
@@ -4921,7 +4920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>297</v>
       </c>
@@ -4953,7 +4952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>297</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>297</v>
       </c>
@@ -5017,7 +5016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>297</v>
       </c>
@@ -5049,7 +5048,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>297</v>
       </c>
@@ -5081,7 +5080,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>297</v>
       </c>
@@ -5113,7 +5112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>297</v>
       </c>
@@ -5146,13 +5145,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K81" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Análisis de gabinete"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{22219FAC-0A92-45F8-A9A9-E7907A117DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{486B0CC1-D3F9-4C94-89FC-37B7419BADD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma_Fase2" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="377">
   <si>
     <t>Sucursal</t>
   </si>
@@ -1458,9 +1458,6 @@
     <t>Expansión/Comité Directivo</t>
   </si>
   <si>
-    <t>Modelo</t>
-  </si>
-  <si>
     <t>2026-04-22</t>
   </si>
   <si>
@@ -1681,6 +1678,9 @@
   </si>
   <si>
     <t>2026-12-11</t>
+  </si>
+  <si>
+    <t>800 por validar</t>
   </si>
 </sst>
 </file>
@@ -2694,16 +2694,16 @@
         <v>71</v>
       </c>
       <c r="E5" s="49" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="F5" s="49" t="s">
-        <v>373</v>
-      </c>
       <c r="G5" s="49" t="s">
+        <v>371</v>
+      </c>
+      <c r="H5" s="49" t="s">
         <v>372</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>373</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2726,13 +2726,13 @@
         <v>90</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F6" s="49" t="s">
         <v>39</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>39</v>
@@ -2758,16 +2758,16 @@
         <v>105</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2790,16 +2790,16 @@
         <v>105</v>
       </c>
       <c r="E8" s="49" t="s">
+        <v>374</v>
+      </c>
+      <c r="F8" s="49" t="s">
         <v>375</v>
       </c>
-      <c r="F8" s="49" t="s">
-        <v>376</v>
-      </c>
       <c r="G8" s="49" t="s">
+        <v>374</v>
+      </c>
+      <c r="H8" s="49" t="s">
         <v>375</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>376</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2822,16 +2822,16 @@
         <v>131</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6954,7 +6954,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -6974,7 +6974,7 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -7014,7 +7014,7 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -7034,7 +7034,7 @@
         <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -7074,7 +7074,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -7094,7 +7094,7 @@
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -7114,7 +7114,7 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -7134,7 +7134,7 @@
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -7151,10 +7151,10 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>310</v>
+      </c>
+      <c r="F13" t="s">
         <v>311</v>
-      </c>
-      <c r="F13" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -7174,7 +7174,7 @@
         <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -7191,10 +7191,10 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" t="s">
         <v>314</v>
-      </c>
-      <c r="F15" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -7211,10 +7211,10 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16" t="s">
         <v>316</v>
-      </c>
-      <c r="F16" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -7231,10 +7231,10 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
+        <v>317</v>
+      </c>
+      <c r="F17" t="s">
         <v>318</v>
-      </c>
-      <c r="F17" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -7251,7 +7251,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F18" t="s">
         <v>37</v>
@@ -7291,7 +7291,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F20" t="s">
         <v>43</v>
@@ -7314,7 +7314,7 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -7334,7 +7334,7 @@
         <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -7374,7 +7374,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -7394,7 +7394,7 @@
         <v>55</v>
       </c>
       <c r="F25" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -7434,7 +7434,7 @@
         <v>39</v>
       </c>
       <c r="F27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -7474,7 +7474,7 @@
         <v>62</v>
       </c>
       <c r="F29" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -7494,7 +7494,7 @@
         <v>64</v>
       </c>
       <c r="F30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -7531,10 +7531,10 @@
         <v>71</v>
       </c>
       <c r="E32" t="s">
+        <v>328</v>
+      </c>
+      <c r="F32" t="s">
         <v>329</v>
-      </c>
-      <c r="F32" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -7551,10 +7551,10 @@
         <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -7571,7 +7571,7 @@
         <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F34" t="s">
         <v>35</v>
@@ -7591,7 +7591,7 @@
         <v>71</v>
       </c>
       <c r="E35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F35" t="s">
         <v>75</v>
@@ -7611,10 +7611,10 @@
         <v>71</v>
       </c>
       <c r="E36" t="s">
+        <v>332</v>
+      </c>
+      <c r="F36" t="s">
         <v>333</v>
-      </c>
-      <c r="F36" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -7631,10 +7631,10 @@
         <v>71</v>
       </c>
       <c r="E37" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F37" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -7654,7 +7654,7 @@
         <v>45</v>
       </c>
       <c r="F38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -7671,7 +7671,7 @@
         <v>71</v>
       </c>
       <c r="E39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F39" t="s">
         <v>80</v>
@@ -7691,7 +7691,7 @@
         <v>71</v>
       </c>
       <c r="E40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F40" t="s">
         <v>83</v>
@@ -7711,7 +7711,7 @@
         <v>71</v>
       </c>
       <c r="E41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F41" t="s">
         <v>86</v>
@@ -7751,7 +7751,7 @@
         <v>90</v>
       </c>
       <c r="E43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F43" t="s">
         <v>40</v>
@@ -7771,10 +7771,10 @@
         <v>90</v>
       </c>
       <c r="E44" t="s">
+        <v>340</v>
+      </c>
+      <c r="F44" t="s">
         <v>341</v>
-      </c>
-      <c r="F44" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -7791,10 +7791,10 @@
         <v>90</v>
       </c>
       <c r="E45" t="s">
+        <v>342</v>
+      </c>
+      <c r="F45" t="s">
         <v>343</v>
-      </c>
-      <c r="F45" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -7811,7 +7811,7 @@
         <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F46" t="s">
         <v>81</v>
@@ -7831,7 +7831,7 @@
         <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F47" t="s">
         <v>84</v>
@@ -7851,7 +7851,7 @@
         <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F48" t="s">
         <v>87</v>
@@ -7871,10 +7871,10 @@
         <v>90</v>
       </c>
       <c r="E49" t="s">
+        <v>347</v>
+      </c>
+      <c r="F49" t="s">
         <v>348</v>
-      </c>
-      <c r="F49" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -7891,10 +7891,10 @@
         <v>90</v>
       </c>
       <c r="E50" t="s">
+        <v>349</v>
+      </c>
+      <c r="F50" t="s">
         <v>350</v>
-      </c>
-      <c r="F50" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -7911,10 +7911,10 @@
         <v>90</v>
       </c>
       <c r="E51" t="s">
+        <v>351</v>
+      </c>
+      <c r="F51" t="s">
         <v>352</v>
-      </c>
-      <c r="F51" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -7934,7 +7934,7 @@
         <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -7951,7 +7951,7 @@
         <v>105</v>
       </c>
       <c r="E53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F53" t="s">
         <v>35</v>
@@ -7971,7 +7971,7 @@
         <v>105</v>
       </c>
       <c r="E54" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F54" t="s">
         <v>38</v>
@@ -7991,10 +7991,10 @@
         <v>105</v>
       </c>
       <c r="E55" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F55" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -8011,10 +8011,10 @@
         <v>105</v>
       </c>
       <c r="E56" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F56" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -8031,10 +8031,10 @@
         <v>105</v>
       </c>
       <c r="E57" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F57" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -8051,10 +8051,10 @@
         <v>105</v>
       </c>
       <c r="E58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F58" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>105</v>
       </c>
       <c r="E59" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F59" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -8091,10 +8091,10 @@
         <v>105</v>
       </c>
       <c r="E60" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F60" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -8111,10 +8111,10 @@
         <v>105</v>
       </c>
       <c r="E61" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F61" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -8151,7 +8151,7 @@
         <v>105</v>
       </c>
       <c r="E63" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F63" t="s">
         <v>41</v>
@@ -8174,7 +8174,7 @@
         <v>60</v>
       </c>
       <c r="F64" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -8194,7 +8194,7 @@
         <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -8251,7 +8251,7 @@
         <v>105</v>
       </c>
       <c r="E68" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F68" t="s">
         <v>87</v>
@@ -8271,10 +8271,10 @@
         <v>105</v>
       </c>
       <c r="E69" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F69" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -8291,10 +8291,10 @@
         <v>105</v>
       </c>
       <c r="E70" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F70" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -8311,10 +8311,10 @@
         <v>105</v>
       </c>
       <c r="E71" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F71" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -8351,10 +8351,10 @@
         <v>131</v>
       </c>
       <c r="E73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -8411,10 +8411,10 @@
         <v>131</v>
       </c>
       <c r="E76" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F76" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -8431,10 +8431,10 @@
         <v>131</v>
       </c>
       <c r="E77" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F77" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -8451,10 +8451,10 @@
         <v>131</v>
       </c>
       <c r="E78" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -8471,10 +8471,10 @@
         <v>131</v>
       </c>
       <c r="E79" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F79" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -8491,10 +8491,10 @@
         <v>131</v>
       </c>
       <c r="E80" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F80" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -8511,10 +8511,10 @@
         <v>131</v>
       </c>
       <c r="E81" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F81" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -8529,7 +8529,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
@@ -8601,12 +8601,10 @@
       <c r="A5" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="3">
-        <v>400</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>302</v>
-      </c>
+      <c r="B5" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="5">
         <v>5000000</v>
       </c>
@@ -8616,8 +8614,8 @@
       <c r="A6" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="3">
-        <v>800</v>
+      <c r="B6" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5">

--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{486B0CC1-D3F9-4C94-89FC-37B7419BADD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{B92AA4D1-3A80-4B37-898B-961413587B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1680,7 +1680,7 @@
     <t>2026-12-11</t>
   </si>
   <si>
-    <t>800 por validar</t>
+    <t>En revision</t>
   </si>
 </sst>
 </file>
@@ -8601,10 +8601,12 @@
       <c r="A5" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="3">
+        <v>800</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C5" s="4"/>
       <c r="D5" s="5">
         <v>5000000</v>
       </c>
@@ -8614,10 +8616,12 @@
       <c r="A6" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="3">
+        <v>800</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C6" s="4"/>
       <c r="D6" s="5">
         <v>9000000</v>
       </c>

--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B92AA4D1-3A80-4B37-898B-961413587B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{3BB1B61D-CCCD-4CBA-A36D-46FD12DC4C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma_Fase2" sheetId="1" r:id="rId1"/>
@@ -3410,7 +3410,7 @@
         <v>56</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>

--- a/Salud_Programa_ABA.xlsx
+++ b/Salud_Programa_ABA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoflosa-my.sharepoint.com/personal/daniel_reynaga_abacentro_com_mx/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{3BB1B61D-CCCD-4CBA-A36D-46FD12DC4C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{FE1B6B9A-D0CE-40D7-AC94-CFC69C0350D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2770,7 +2770,7 @@
         <v>354</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>
@@ -3410,7 +3410,7 @@
         <v>56</v>
       </c>
       <c r="I27">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>
@@ -3922,7 +3922,7 @@
         <v>59</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43" t="s">
         <v>30</v>
